--- a/regulatory-compliance/cloud-foundation/9.1/eu-cloud-sovereignty/vcf-91-companion-eu-cloud-sovereignty.xlsx
+++ b/regulatory-compliance/cloud-foundation/9.1/eu-cloud-sovereignty/vcf-91-companion-eu-cloud-sovereignty.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="190" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Version 910-20260612-01</t>
+          <t>Version 910-20260623-01</t>
         </is>
       </c>
     </row>
@@ -536,17 +536,16 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Disclaimer</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Additional Resources</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
-This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+          <t>This is one of a library of companion guides that map VMware Cloud Foundation and its advanced services to security and compliance frameworks. For each framework, the guide is published as a spreadsheet, a CSV data file, a Markdown document, and a PDF, together with a Security Configuration Guide crosswalk that identifies the VCF technical hardening settings relevant to that framework. The companion guide library, the VMware Cloud Foundation Security Configuration Guide, and related security documentation, sample scripts, and Q&amp;A are available at https://brcm.tech/vcf-security.</t>
         </is>
       </c>
     </row>
@@ -554,12 +553,28 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
+This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Copyright (c) CA, Inc. All rights reserved.
 You are hereby granted a non-exclusive, worldwide, royalty-free license under CA, Inc.'s copyrights to use, copy, modify, and distribute this software in source code or binary form for use in connection with CA, Inc. products.
@@ -568,16 +583,16 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Third Party Identifiers and Mappings</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>This document includes regulatory compliance and security control identifiers from external sources as a convenience to end users. This does not constitute endorsement, in either direction.
 There is not a one-to-one mapping of product capabilities to third-party controls. A product capability, or set of capabilities, may be applicable to multiple controls. Conversely, a control may be satisfied with the use of multiple capabilities.
@@ -886,29 +901,10 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>VCF implements cryptographic protections across its component stack using publicly standardized, validated cryptographic modules and algorithms.
-Multiple VCF components rely on cryptographic modules validated through the NIST Cryptographic Module Validation Program (CMVP) to FIPS 140-2 and FIPS 140-3 standards. NSX is configured to use FIPS 140-3 validated cryptographic modules by default, and NSX Manager uses FIPS 140 approved algorithms for authentication to its cryptographic module. Specific NSX validated modules include IKE with Rambus Safezone 2.0 (Certificate #4898), VMware OpenSSL 3.0.9 (Certificate #4861), VMware BouncyCastle 2.0.0 (Certificate #4986), and VMware BoringCrypto 6.0 (Certificate #4694). VCF Automation uses the BouncyCastle FIPS 2.0.0 cryptographic module, which holds FIPS 140-3 Certificate #4743. VCF Operations for Networks uses BC-FJA (Bouncy Castle FIPS Java API) version 2.0.0 with FIPS 140-2 Certificate #37009 as its validated cryptographic module. This consistent use of FIPS-validated modules across the platform means that organizations deploying VCF in regulated environments can rely on cryptographic implementations that have undergone independent validation against well-known public standards. The VMware Kubernetes Service (VKS) consumption layer also supports FIPS mode: VKS ClusterClass configurations include a fips.enabled variable that, when set, restricts cryptographic operations on cluster nodes to approved algorithm implementations. FIPS-enabled Kubernetes release images, identified by a -fips suffix in the release reference name, are available for organizations that require FIPS-validated cryptography across their containerized workloads.
-At the protocol and algorithm level, VCF enforces modern cryptographic standards throughout. Starting in vSphere 9.0, all TLS profiles are FIPS compliant; the COMPATIBLE profile supports modern TLS cipher suites with standardized elliptic curves. Monitoring infrastructure such as Telegraf enforces a modern TLS minimum version for secure communication. The NSX L2 VPN FIPS compliance suite uses AES-GCM encryption with Perfect Forward Secrecy and Diffie-Hellman Group 20. NSX also supports ECDSA (Elliptic Curve Digital Signature Algorithm) encryption for environments with high-assurance cryptographic requirements. VCF Operations for Networks supports several encryption algorithms and ciphers for its data sources. VCF Operations provides a FIPS Security Mode that, when enabled, applies additional algorithm and cipher prerequisites across the management domain. All system management network communications are encrypted by default using standardized cipher suites. At the VKS layer, Kubernetes control plane components expose parameters for restricting permitted TLS configurations: the kube-apiserver --tls-cipher-suites parameter, the kubelet tlsCipherSuites configuration field, and the equivalent parameter on the kube-scheduler each restrict the set of permitted cipher suites, allowing administrators to exclude deprecated or weak algorithms. The kubelet tlsMinVersion field and the --tls-min-version parameter on the kube-apiserver enforce a minimum TLS protocol version floor for inbound connections. The Antrea networking component and vSphere Cloud Provider Interface on VKS clusters also support configurable TLS cipher suites for component-to-component communication. Kubernetes hardening guidance identifies specific preferred cipher suites and calls out cipher suite configuration on the kube-scheduler as a required hardening step. VKS clusters support the Istio service mesh package, which provides mutual TLS between workloads within the mesh; the meshMTLS.minProtocolVersion setting controls the minimum protocol version for inter-service communication, defaulting to TLS 1.2 with support for configuring TLS 1.3.
-Data-in-transit protections using TLS have customizable PKI keypair and certificate options. These range from fully automated within VCF to semi-automated using certificates from enterprise PKI infrastructure or fully custom certificates installed manually. Automated certificate issuance is supported with Microsoft Active Directory Certificate Services. Trust establishment uses standard PKI management with multiple certificate options including Root CA certificates, CSR-based certificates, and direct certificate uploads. VCF Operations provides centralized certificate lifecycle management for all VCF components, enabling automated certificate renewal, monitoring, and replacement across the infrastructure. Organizations should be aware that if self-signed certificates and private keys are generated using OpenSSL, those certificates and private keys are not FIPS-compatible. Environments operating under FIPS requirements should use certificate authorities and key generation methods that produce FIPS-compliant artifacts. For FIPS environments, certificates should use key sizes of 2048 or 3072 bits; key sizes greater than 3072 bits have not been tested with FIPS. At the VKS layer, the cert-manager package manages the lifecycle of certificates issued to workloads and ingress endpoints. VKS clusters maintain TLS certificates for component-to-component communication across their control and data planes. The Contour ingress package supports minimum TLS version configuration through the tls.minimum-protocol-version parameter. Harbor, when deployed as a Supervisor Service, accepts custom TLS certificate configuration through the tlsCertificate.tls.crt and tlsCertificate.tls.key fields, allowing organizations to supply certificates from their enterprise certificate authority rather than relying on self-signed certificates. The Supervisor secret injection agent automatically configures mutual TLS for communication with the vault-agent-injector service using auto-generated certificates.
-Data-at-rest encryption uses vSAN cluster-based encryption or VM Encryption on non-vSAN storage. vSAN encryption uses AES-NI CPU offloading for efficient processing, and VMware ESX hosts encrypt vSAN disk data using the industry standard AES-256 XTS mode. Encryption keys are managed through KMIP 1.1-compatible external Key Management Servers (KMS) or vSphere Native Key Provider (NKP), which is included in all vSphere editions and does not require an external key server. VCF implements a three-element domain of trust comprising the key provider, VMware vCenter, and vSAN hosts. Key Encryption Keys (KEK) wrap Disk Encryption Keys (DEK) for secure key management; ESX hosts use the KEK to encrypt their internal keys and store only the encrypted internal keys on disk, not the KEK itself.
-VCF Standard Key Providers have key wrapping capabilities that let organizations store a single wrapping key in their KMS, protecting multiple Key Encryption Keys within the VCF environment. This creates a three-tier key hierarchy: the Data Encryption Key encrypts object data, the Key Encryption Key protects the DEK, and the wrapping key protects the KEK. This approach reduces the number of keys stored in external KMS systems while maintaining cryptographic separation. Key wrapping includes automatic key rotation with configurable intervals from 30 days to 10 years.
-With key persistence enabled, ESX hosts can persist encryption keys in the Trusted Platform Module (TPM) across reboots, allowing encryption operations to continue when the key server is unavailable. Each ESX host obtains the encryption keys initially and retains them in its key cache; if the ESX host has a TPM, the encryption keys are persisted in the TPM across reboots. Key persistence can be enabled using the esxcli system security keypersistence enable command.
-VCF supports guest-level security features including virtual Trusted Platform Module (vTPM) 2.0 for VMs. This enables in-guest encryption capabilities such as Windows BitLocker, Linux disk encryption, and other operating system-native security features. Secure Boot provides UEFI verification to help ensure only signed and trusted code runs during the VM boot process. These features work independently of or in combination with infrastructure-level encryption, allowing organizations to implement defense-in-depth strategies.
-vSAN offers Data-in-Transit (DIT) encryption as a cluster-wide setting that encrypts all data and metadata traffic as it transits across hosts. For vSAN Original Storage Architecture (OSA), data-at-rest encryption occurs at the Local Object Manager (LSOM) layer on the target host, making DIT encryption strongly recommended to restrict network-level interception. For vSAN Express Storage Architecture (ESA) in HCI mode, data is encrypted at the VM host before network transmission, making DIT encryption optional based on compliance requirements and risk tolerance. DIT encryption operates without requiring external key management servers and provides independent key rotation from data-at-rest encryption.
-Encrypted vSphere vMotion secures confidentiality, integrity, and authenticity of data transferred during VM migrations. For encrypted VMs, vMotion always uses encryption. For unencrypted VMs, encrypted vMotion can be set to Disabled, Opportunistic (default), or Required. Cross-vCenter vMotion is supported when using shared key providers or backup/import of Native Key Provider. VCF uses one-time keys (nonces) for each migration session so that captured traffic cannot be replayed or decrypted after migration completes.
-Memory Tiering encryption provides protection for tiered memory without requiring external key management. VCF generates random 256-bit AES-XTS keys at the kernel level during VM power-on, unique to each VM instance or per host depending on configuration.
-VM Encryption provides protection across all datastore types including vSAN, iSCSI, NFS, and Fibre Channel. Disk encryption uses XTS-AES-256 keys as the disk encryption key. This encryption occurs before data reaches the storage layer, providing both data-at-rest and data-in-transit protection.
-Kubernetes on VKS supports encryption at rest for data stored within the control plane. Operators configure the encryption provider and manage key access for control plane secrets; when relying on a managed key provider, administrators retain responsibility for access controls over the managed key material. The VCF Automation consumption layer includes VCF Encryption Management, which grants organization administrators the ability to use encryption keys from their own key providers for encryption of virtual machines and disks in their VCF environment, extending the platform's cryptographic key management to tenant-level operations.
-For storage protocols, VCF provides varying levels of native encryption support. iSCSI includes CHAP for session authentication. Fibre Channel Gen 7 supports end-to-end encryption with secure HBAs. For NFS datastores, version 4.1 supports Kerberos authentication with three security levels: krb5 (authentication only), krb5i (authentication plus integrity checking), and krb5p (authentication plus privacy with full encryption).
-ESX stores configuration data in encrypted form on boot devices. When the host has a TPM 2.0 enabled and configured, the configuration encryption key is stored in the TPM. The encryption mode can be configured using the esxcli system settings encryption set command with the --mode=TPM parameter.
-Cryptographic operations are controlled through fine-grained privileges in vCenter. Only users assigned the Cryptographic Operations privileges can perform cryptographic operations. A dedicated No Cryptography Administrator role enables standard VM and infrastructure management while restricting unauthorized encryption changes. This role can be cloned and customized to grant only specific Cryptographic Operations privileges, such as allowing encryption but not decryption, supporting the principle of least privilege for encryption tasks. The CryptoManager and CryptoManagerKmip managed objects provide programmatic interfaces for handling cryptographic keys and integrating with key management server infrastructure. vSAN encryption key management requires specific permissions including Cryptographer.ManageEncryptionPolicy, Cryptographer.ManageKeyServers, and Cryptographer.ManageKeys.
-vSAN includes secure disk wipe capabilities for proper media sanitization when decommissioning storage, supporting the Erase disks before use option during encryption configuration and disk management operations.
-Defining the organization's cryptographic policy (algorithm selection, key strength, rotation schedules, KMS architecture, FIPS-mode activation decisions) and the key lifecycle management standards that govern key creation, distribution, storage, archive, and destruction sit with the organization above the platform. VCF supplies the validated cryptographic modules and protocol enforcement; the organizational cryptographic governance program determines how those mechanisms apply across the environment. Security Technical Implementation Guides (STIGs) for Supervisor and VKS releases are available to guide cryptographic hardening of the consumption layer.
-VMware Private AI Services (PAIS) provides cryptographic controls across its AI infrastructure components, building on the cryptographic foundation of VCF.
-GPU-accelerated VMware Kubernetes Service (VKS) clusters deployed for PAIS workloads use a FIPS-enabled Kubernetes runtime. The VKS cluster topology version applied to both control plane and worker deployments uses a FIPS-enabled VKR build running on Ubuntu 24.04, so AI workloads on PAIS VKS clusters operate within a FIPS-compliant Kubernetes runtime.
-PAIS endpoints use TLS for service communication. The PAISConfiguration custom resource supports configurable CA bundle references through spec.clientTls.caBundleRefs for OIDC provider and Harbor registry authentication. The Supervisor endpoint communication for PAIS uses HTTPS on port 6443 with certificate-based authentication. The PAIS Prometheus metrics endpoint uses self-signed certificate authentication with TLS, where the CA certificate is retrieved from the pais-ingress-default Secret in the PAIS namespace and configured in base64-decoded form. Prometheus TLS client authentication and certificate validation are off by default; auditors should verify that client authentication is enabled in production deployments where mutual certificate validation is required.
-PAIS requires CA trust bundles to be configured for all external HTTPS connections, including OIDC providers, Harbor registries, content management systems used as data sources in the Data Indexing and Retrieval service (such as Confluence or SharePoint), MCP servers that provide tools to agents, and the pgvector database server used for vector storage. Trust bundle material is obtained from each external system's administrator either as a certificate file or as a ConfigMap stored in the namespace where PAIS is deployed, and PAIS recommends maintaining separate trust bundles per application with periodic updates before certificate expiration. Administrators add trusted certificates through the VCF Automation Provider Management UI under Certificate Management and Trusted Certificates. The issuer certificate of the Harbor registry must also be added to the certificate trust store on Deep Learning VMs that pull models from the registry. When connecting to an MCP server over HTTPS, the MCP server issuer certificate must be added as a CA trust bundle.
-The underlying cryptographic algorithms, cipher suites, and platform-level key management are provided by VCF and VKS. Organizations are responsible for selecting and enforcing approved cryptographic standards at the VCF and infrastructure level, while PAIS provides the certificate management and trust chain configuration mechanisms specific to AI service endpoints.</t>
+          <t>VMware Private AI Services (PAIS) provides provenance tracking mechanisms for model artifacts and data sources used by AI workloads. Models are stored in Harbor registries integrated with PAIS as a model storage backend, with authentication and certificate-based trust required for model retrieval. PAIS is also compatible with OCI-compliant registries from other vendors, allowing organizations to use existing model storage infrastructure while preserving artifact lineage. Each model artifact stored as an OCI object carries an immutable manifest and a unique content digest, which provides verifiable lineage from a deployed model back to its specific revision and the registry of origin.
+In disconnected (air-gapped) environments, a Harbor registry acts as a controlled intermediary between external model sources and the internal deployment environment. The artifact mirroring tool (AMT), distributed as part of the pais CLI plug-in, helps administrators populate the Harbor registry from external sources before catalog publication. PAIS requires HTTPS trust bundles configured for the OIDC provider, the Harbor registry, content management systems hosting knowledge base data, and Model Context Protocol servers providing tools to models, which establishes verified channels for the artifact and data sources entering the platform.
+For knowledge base data used in retrieval-augmented generation, PAIS Data Indexing and Retrieval connects to enterprise content management systems such as Microsoft SharePoint sites and Amazon S3 compatible stores as data sources. Data sources are created with a specific type that cannot be changed after creation, and a knowledge base can be linked to a maximum of ten data sources, with one data source linkable to multiple knowledge bases. PAIS tracks document-level changes during indexing operations, capturing counts of crawled documents, new documents found, deleted documents, existing unmodified documents, modified documents requiring embeddings update, and skipped documents. Indexing operations also record megabytes downloaded, number of new chunks indexed, final index size after removal of deleted documents, and timing metrics for download, embedding generation, and the index operation. PAIS supports OpenTelemetry collector integration for metrics collection and large language model traces, including knowledge base indexing traces, which records observable evidence of content provenance at the data layer.
+PAIS gives a foundation for content provenance through OCI-based artifact immutability and digest-based integrity verification, combined with knowledge base indexing telemetry. The platform does not implement a formal content provenance benchmarking standard such as SLSA (Supply Chain Levels for Software Artifacts) or SPDX (Software Package Data Exchange). Organizations requiring benchmarking against industry-recognized provenance standards layer those frameworks on top of PAIS-native artifact and data source management.</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
@@ -918,14 +914,10 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to the implementation of cryptographic protection controls by using known public standards and trusted cryptographic technologies across its component stack for securing inter-component communications and providing cryptographic inspection capabilities for network traffic.
-Security Services Platform (SSP), the control-plane component of vDefend, secures communications between vDefend product components using certificates and current TLS protocol versions with approved cipher suites. SSP and the SSP Installer deploy with the most current TLS version by default and also support the prior major TLS version. The TLS versions and cipher suites allowed on SSP Installer and SSP are fixed and cannot be modified, which enforces a consistent cryptographic baseline across deployments.
-SSP components, including the SSP Installer and the NDR Sensor for vDefend, implement FIPS 140-2 and FIPS 140-3 cryptographic module standards. SSP uses the VMware BouncyCastle Module (NIST CMVP Certificate #4943) and the VMware OpenSSL FIPS provider Object Module (NIST CMVP Certificate #4861) for its cryptographic operations. SSP actively enforces cryptographic hygiene by rejecting any certificate or TLS configuration that uses deprecated algorithms, short keys, or legacy protocol versions, returning a validation error rather than permitting degraded connections.
-Certificate management within SSP provides lifecycle controls including certificate export, certificate signing request (CSR) generation, and CA-signed certificate replacement. SSP monitors and manages several certificate types used to identify client and host machines, establish trust between components, secure communications, and control access levels. Administrators can retrieve and validate LDAP certificates using standard tools to establish secure LDAPS connections for platform authentication. These capabilities allow organizations to integrate vDefend into their broader PKI infrastructure and follow standard certificate lifecycle practices.
-vDefend provides TLS Inspection capabilities that allow the firewall to decrypt, inspect, and re-encrypt TLS-protected traffic. Without TLS Inspection, encrypted traffic cannot be examined or enforced against security policies even when other advanced security features are enabled. With TLS Inspection enabled, vDefend gains visibility into encrypted traffic flows, supporting more effective access control and threat detection. TLS Inspection also supports importing or generating trusted and untrusted proxy certificate authorities for external decryption profiles, giving administrators control over the CA chain used in inspection.
-TLS Inspection includes a Crypto Enforcement option within decryption action profiles that allows administrators to set minimum and maximum protocol version and cipher suite constraints for both client and server connections. Profiles can be configured in Transparent or Enforce modes; the Enforce mode requires compliance with the configured cryptographic constraints.
-vDefend IDS/IPS signature rules extend cryptographic visibility by supporting protocol version matching and certificate Subject field matching, enabling enforcement decisions based on certificate metadata in encrypted traffic. IDS/IPS rules also support storing TLS/SSL certificates to disk for forensic analysis and threat investigation. SSP guidance recommends that organizations restrict or block protocols that carry data in cleartext and enforce minimum secure protocol versions as part of their network security practices.
-vDefend does not itself provide the underlying key management infrastructure (KMS), platform-wide PKI lifecycle management, or the broader VCF platform's cryptographic controls; those responsibilities belong to VCF. However, vDefend's consistent use of approved cryptographic standards for its own operations and its ability to perform cryptographic inspection of network traffic contribute to an organization's overall implementation of cryptographic protection controls.</t>
+          <t>VMware vDefend (vDefend) contributes to constraining the impact of digital sovereignty laws through GeoIP visibility, IDS/IPS-based geographic detection, distributed firewall scoping, and federated policy management at the network layer.
+vDefend's Security Services Platform includes GeoIP Monitoring, which displays a map of network traffic to and from every country in the world. This capability requires the Security Services Platform to be deployed with the metrics feature enabled and gives administrators visibility into geographic traffic patterns across the environment. vDefend IDS/IPS signature rules support geoip matching on source IP addresses, destination IP addresses, or both, providing a detection mechanism that identifies traffic associated with specific countries within east-west distributed traffic flows. This allows administrators to detect and respond to data flows that cross jurisdictional boundaries where policy requires them to remain local.
+vDefend supports policy scoping across global, regional, and local spans in a federated deployment. Security Services Platform regions can be associated with Security and Network policies to control policy scope across multiple locations. DFW policies applied globally allow sources or destinations to be any object without span restrictions, while the Applied To field scopes enforcement to specific zones, tenants, or applications without affecting policies defined for other workloads. This regional policy architecture allows organizations to define distinct security controls for workloads in different jurisdictions while maintaining a consistent baseline across sites. In a federated environment, malicious traffic can be blocked across Local Managers from the Global Manager, providing centralized enforcement across geographically distributed sites.
+These network-layer capabilities complement the broader VCF data sovereignty mechanisms, including encryption and workload placement constraints, by providing traffic-level controls and visibility that support geographic boundary enforcement. Defining organizational data residency policies, mapping regulatory requirements to specific network policies, and managing contractual obligations around data localization remain organizational responsibilities outside vDefend's scope.</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr">
@@ -935,11 +927,10 @@
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) implements cryptographic protections for disaster recovery workflows using known public standards and trusted cryptographic technologies.
-PNR uses modern TLS by default for all connections to the PNR server. The minimum TLS protocol version is configurable through the envoy-proxy-config.json file by editing the tls_minimum_protocol_version parameter. When the minimum protocol version is modified, PNR requires that the change be applied consistently across all relevant configuration occurrences in the system. Administrators can verify the TLS version in use on the Site Recovery Manager component using standard OpenSSL tooling.
-The PNR Appliance requires an SSL/TLS certificate as the endpoint certificate for all TLS connections to the PNR server. PNR supports custom certificates signed by a certificate authority as an alternative to self-signed certificates. Custom SSL/TLS server endpoint certificates must meet specific requirements, including x509v3 Extended Key Usage indicating TLS Web Server Authentication. The Appliance Management Interface allows administrators to import CA-signed server certificates and custom root CA certificates, and to replace the appliance certificate. PNR uses TLS certificates and private keys to protect network communication and establish authentication with other servers. Certificate verification error messages are logged in security-related log files, and operational log files do not contain sensitive information such as private keys or passwords.
-For encrypted virtual machine replication, PNR requires that the recovery and protected sites use a common Key Management Server (KMS) or that the KMS clusters at both sites share common encryption keys. Replication of encrypted virtual machines also requires Secure LWD support to be available on the virtual machine. This supports data-at-rest encryption continuity for virtual machines through the recovery lifecycle.
-Defining the organization's cryptographic policy, including KMS architecture decisions, minimum TLS version selection, certificate management standards, and key lifecycle practices, sits with the organization above the DR layer. PNR supplies the cryptographic mechanisms needed for DR-specific traffic and operations; the organizational cryptographic governance program determines how those mechanisms apply across the environment.</t>
+          <t>VCF Protection and Recovery (PNR) and vSphere Replication maintain control of cryptographic keys for encrypted material stored or transmitted across sites through the VCF platform's layered key management architecture.
+PNR and vSphere Replication require matching key provider configurations at both protected and recovery sites. Encrypted virtual machines cannot be replicated to a remote site unless that site has access to the appropriate encryption keys through a common KMS or vSphere Native Key Provider. This requirement means encrypted material cannot be moved to an external system without the organization explicitly providing key access, maintaining organizational control over the key-to-data relationship. When using the vSphere Native Key Provider, the provider ID configured on the local site must match the provider ID on the remote site, confirming key identity before replication proceeds.
+When replication seeds are used, replica disks can have different encryption keys from the source disks, but the key management infrastructure at the recovery site still controls access to those keys. The vSphere Replication appliance automatically installs an encryption agent on source ESX hosts for replication encryption, with key material managed through the platform's key infrastructure rather than embedded in the replication stream. When replication of an encrypted virtual machine is configured, encryption of transferred data is automatically enabled and cannot be disabled, so encrypted machines do not transit unprotected across site boundaries.
+The VCF platform provides the underlying key separation architecture. Key Encryption Keys (KEK) wrap Data Encryption Keys (DEK), and the KEK is not stored on the ESX host, maintaining separation between encryption keys and encrypted data. Internal keys are kept in memory only during operations. Fine-grained Cryptographic Operations privileges control which identities can perform key operations, and the vSphere Native Key Provider operates without sending keys to an external system. Site Recovery Manager (SRM) supports FIPS mode activation, which restricts cryptographic operations to approved algorithms through the BouncyCastle FIPS provider.</t>
         </is>
       </c>
       <c r="K4" s="10" t="inlineStr">
@@ -949,12 +940,11 @@
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) implements cryptographic protections across multiple layers of its architecture, applying standard cryptographic technologies for data in transit, certificate trust management, and credential storage.
-Starting with DSM, the platform enforces FIPS 140-3 compliant cryptographic standards and validates certificates during upload, rejecting unsupported algorithms or parameters. Only RSA and ECDSA public key algorithms are accepted for certificates. The Ed25519 elliptic curve signature algorithm is rejected because it does not comply with FIPS 140-3. Custom trusted certificates should use ECDSA P-256 or P-384 algorithms; RSA certificates must meet a minimum key size of 2048 bits per FIPS requirements. DSM's latest certificate validation mode enforces strict cryptographic and KeyUsage validations across all DSM endpoints, including the Provider VM and data service clusters.
-For connections to database clusters, DSM requires TLS for all client traffic. PostgreSQL database instances enforce a minimum TLS protocol version through the ssl_min_protocol_version setting. MySQL enforces minimum TLS versions on both the main connection interface and the administrative interface; these settings are fixed and cannot be modified by users, which helps maintain a consistent cryptographic baseline across deployments. MySQL also exposes the group_replication_recovery_tls_version setting to specify the TLS protocol used during distributed recovery connections. DSM supports SQL Server clusters, which use TLS to encrypt communication between clients and the cluster; the network.tlsProtocols custom engine setting defines the allowed TLS versions for client connections, and a minimum TLS version must be included for the DSM operator to manage the cluster. DSM supports TLS verification during PostgreSQL database migration, covering replication traffic between source and target clusters.
-DSM's certificate management capabilities support standard PKI practices. Administrators configure custom TLS certificates for database clusters through the DSM UI or API, providing certificates in PEM format with associated private keys and CA certificates. Supported private key algorithms are RSA and ECDSA with key sizes of 256 and 384 bits. When present, the X509v3 KeyUsage extension on a custom certificate must include the DigitalSignature capability; DSM also accepts certificates that omit the KeyUsage extension entirely, treating absent KeyUsage as permitting all usages in accordance with RFC 5280. To establish secure connections to database clusters and to the DSM Provider VM, clients add the CA to the operating system trust store or the trusted CA list. DSM's API provides a mechanism to retrieve the CA certificate from a custom certificate secret. The Consumption Operator, which enables self-service database provisioning, requires a TLS certificate for its communication with the DSM provider. Certificate management can also be handled through Kubernetes cert-manager, which manages various issuer types and outputs Kubernetes TLS Secrets in the format DSM requires.
-DSM supports TLS for connections to external systems. When configuring log forwarding to an SMTP server, DSM supports Auto TLS to establish a secure connection. For private container registries, DSM supports CA certificate validation for untrusted registries.
-For local user credential storage, DSM encrypts passwords using PGP symmetric encryption through the PGCrypto library, with dedicated encryption keys stored using the PGCRYPTO_PASSWORD and PGCRYPTO_ALGORITHM keys. MySQL has FIPS mode available on the client side through the ssl_fips_mode setting. PostgreSQL databases include the pgcrypto extension, which provides cryptographic functions that applications can use directly within the database. The DSM Provider Appliance includes virtual machine encryption, which activates when a Key Management Server is configured in the environment.</t>
+          <t>VMware Data Services Manager (DSM) provides audit logging at both the platform and database levels, giving administrators visibility into privileged actions taken across the system.
+At the platform level, DSM generates system audit events for all user actions performed through the DSM UI and API, as well as actions that DSM itself initiates. These events are accessible through the System Audit Events view in the Provider interface, which is the only DSM UI location for tracking non-database-related operations and tasks. Each audit log entry records an Event Type field that identifies the category of operation performed, an Event Details column that captures operation-specific information, and a Source field that distinguishes user-initiated events (recorded by the user's email address) from events initiated by DSM without user intervention (recorded as "System"). Audit event data can be exported in CSV and XLSX formats for offline review or integration with external audit processes. Gateway Audit Logs provide an additional layer of visibility into gateway-level operations, with export capability covering all events visible to the reviewing user regardless of pagination limits.
+At the database level, PostgreSQL instances provisioned by DSM include the pgaudit extension, which delivers audit logging functionality across all supported PostgreSQL versions. This extension supports auditing of database-level privileged operations including stored procedures and other SQL-level actions. For MySQL databases, DSM enables the log_bin_trust_function_creators configuration setting, which governs logging behavior for stored function creators and their associated binary log entries. For SQL Server databases, DSM supports the standard T-SQL CREATE AUDIT and CREATE AUDIT SPECIFICATION DDL statements for defining custom database audits. DSM can also automatically create a simple audit for login events based on the Login Auditing option selected when creating a SQL Server cluster. The cluster administrator login is granted restricted read-only privileges and specific ALTER privileges for server management and auditing, limiting the scope of administrative access within SQL Server.
+DSM Administrator and User roles can generate database VM logs for monitoring and audit purposes. The Permissions view in the Administrator UI supports the creation, monitoring, and management of configured users, helping administrators identify which accounts hold elevated access within the DSM environment.
+DSM provides the technical mechanisms to capture audit records of privileged actions at the platform and database levels. Organizations remain responsible for defining what constitutes a privileged function for their specific environment, establishing processes for reviewing audit records, configuring forwarding to a centralized log management or SIEM system, and assigning responsibility for ongoing audit review. The audit trail DSM produces supports those organizational processes but does not substitute for them.</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
@@ -964,12 +954,15 @@
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides configurable SSL/TLS profiles that control which cipher suites, protocol versions, and key exchange algorithms are permitted for application traffic termination. The SSL/TLS Profile, configured under Templates &gt; Security &gt; SSL/TLS Profile, contains the accepted protocol version list and a prioritized cipher suite list applied to virtual services. Administrators can create custom profiles or select from built-in templates; the documentation notes that the choice of accepted ciphers and protocol versions involves trade-offs between security, client compatibility, and computational expense. SSL profiles in 9.1 include a Post Quantum Cryptography section with support for modern cipher suites. Controller SSL/TLS certificates support elliptic curve (EC) or RSA algorithms, with EC recommended for new deployments.
-For environments subject to cryptographic module validation requirements, Avi supports a FIPS mode backed by the OpenSSL FIPS Provider, which has been validated at FIPS 140-3 Security Level 1 and awarded Certificate #4985 by the Cryptographic Module Validation Program (CMVP). When FIPS mode is activated on the Controller cluster, Avi restricts cryptographic operations to FIPS-compliant algorithms only. FIPS 140-3 also requires stricter handling of sensitive security parameters including keys, authentication data, and random number generation. FIPS mode is enabled at the Controller cluster level through the Controller settings. Note that FIPS mode does not support SSL Client Hello events in Avi DataScript, which may affect certain scripted traffic inspection use cases.
-Avi Controller allows administrators to restrict specific key exchange algorithms and ciphers for management session access. The Allowed Ciphers field restricts management session ciphers to a specified subset, and the kex_algorithm_exclude field under Controller Settings excludes specific key exchange methods for SSH-based administrative access. Internal communications between the Avi Controller and Service Engines also use SSL/TLS, and custom certificates can be selected for this Secure Channel connection via the Access tab certificate field.
-For certificate management, Avi integrates with Hardware Security Modules (HSMs), including the Thales Luna (formerly SafeNet Luna) HSM, for cryptographic key storage and management. The Controller is set up as an HSM client and can create keys and certificates directly on the HSM through client libraries, supporting high-availability HSM configurations. Automated certificate lifecycle management is available through Let's Encrypt integration using the ACME protocol. Avi's App Transport Security feature supports integration with the Venafi Trust Protection Platform for certificate administration across tenants, with the Trust Protection Platform pushing signed certificates and required chain certificates to Avi Load Balancer.
-For Kubernetes deployments, the Avi Kubernetes Operator (AKO) supports PKIProfile-based certificate validation and trust management for backend services. The PKIProfile, configured through custom resources, enables secure communication with backend services through certificate-based authentication and encryption. In VCF environments, the Avi PKI Profile defines the list of trusted certificate authorities permitted to sign client certificates and can be used to implement Zero Trust security between servers and clients.
-Data-at-rest encryption for Avi Controller and Service Engine VMs is provided by VCF at the platform layer, not by Avi itself. Organizations must configure Avi SSL/TLS profiles, select appropriate cipher suites, and enable FIPS mode where cryptographic module validation requirements apply to activate these controls.</t>
+          <t>VMware Avi Load Balancer (Avi) provides mechanisms that help organizations maintain control of cryptographic keys for TLS certificates and encrypted material, through Hardware Security Module (HSM) integration, external key management service support, and role-based access controls over private key handling.
+Avi Controller integrates natively with Thales Luna Network Hardware Security Modules for cryptographic key storage and management. When HSM integration is configured, the Controller acts as a client of the HSM and can create RSA and EC key pairs and certificates directly on the HSM device, keeping private key material in hardware under the organization's control rather than in the Avi software configuration store. High availability across multiple HSM devices is optionally configurable. The HSM settings are accessible through the Controller's security certificate management interface.
+For cloud deployments, Avi supports customer-managed keys through external key management providers. In AWS environments, the Controller supports customer-managed Customer Master Keys (CMKs), which the organization creates, manages, and rotates. KMS key access can be scoped to a specific key ID or governed through the KMS key policy directly, restricting permissions to the fewest principals necessary. An IAM policy template is available to create and attach the required KMS access policy to the appropriate IAM role. For SNS-SQS encryption, the key policy must grant the SNS service permission to use the CMK with the required KMS actions.
+In GCP environments, Avi accepts customer-supplied Cloud KMS key IDs for encryption of Service Engine disks, Service Engine images, GCS buckets, and GCS objects, each configurable with a separate key in the GCP Cloud Configuration section of the deployment settings. This allows the organization to maintain distinct KMS keys for each storage resource type under its own key management infrastructure.
+For TLS private keys stored in the Avi Controller configuration store, Avi's RBAC system controls which administrators have the ability to export private keys, restricting that capability to the fewest administrators necessary. This is managed through the Controller's user and role administration interface. Avi also supports importing encrypted private keys via CLI for certificate installation.
+Avi Controller allows selection of custom certificates for the encrypted management channel between the Controller and Service Engines, giving organizations control over the certificates used for internal control-plane communication. For VCF deployments, Avi Controller SSL/TLS certificates support both elliptic curve cryptography (EC) and RSA algorithms, with EC recommended.
+For Kubernetes environments, the Avi Kubernetes Operator (AKO) supports configuration of both RSA and ECC signed certificates simultaneously on a virtual service through the alt.crt and alt.key fields, providing flexibility in certificate algorithm selection for ingress workloads.
+Avi Controller and Service Engine support configuration of SSH key exchange algorithms, allowing administrators to exclude weaker key exchange methods for management connections.
+When deployed in FIPS mode, Avi uses a FIPS 140-3 validated cryptographic module, which restricts cryptographic operations to approved algorithms and requires stricter handling of keys, authentication data, and random number generation.</t>
         </is>
       </c>
     </row>
@@ -1001,16 +994,15 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
+          <t>VCF provides several technical capabilities that support the use of industry-recognized virtualization formats, standardized deployment mechanisms, and change-tracking processes, helping organizations maintain interoperability across their cloud infrastructure.
+VCF natively supports the Open Virtualization Format (OVF), an industry standard that describes virtual machine image metadata in an XML format. OVF provides a vendor-neutral, portable way to package and distribute virtual machines, enabling interoperability between different virtualization platforms and cloud environments. OVF templates can be captured from virtual machines or vApps and stored in content libraries for consistent deployment. Content libraries support importing .ovf and .ova files, and the deployment specification for these templates supports optional guest operating system and hardware customization specifications applied during the deployment process. OVF templates from content libraries also become available in Kubernetes namespaces as VM images, allowing DevOps teams to self-service virtual machine provisioning through standard Kubernetes tooling. VMware Kubernetes Service (VKS) distributes Kubernetes node images as vSphere Kubernetes releases (VKrs) in the Open Virtualization Appliance (OVA) format, versioned according to standard Kubernetes versioning conventions. Each VKr documents its OS base (PhotonOS or Ubuntu) together with any vSphere-specific customizations and optimizations, making the scope of custom changes explicit and reviewable; legacy VKrs carry explicit backward-compatibility bounds to prior vSphere versions rather than leaving compatibility scope implicit. The VCF Image Baker supports customization of virtual machine hardware version through configurable OVF properties at build time, allowing organizations to produce node images aligned with their hardware baseline requirements. Guest operating system customization specifications are also stored in XML format and can be exported and imported through the VMware vCenter Customization Specification Manager, providing a portable mechanism for sharing standardized guest OS configurations across vCenter instances.
+VCF enforces standardized virtual hardware through a defined set of hardware versions. The HardwareTypes.Version class defines the valid hardware versions available for virtual machine configuration, and virtual machine CPU and memory configuration ranges are constrained based on the guest operating system and the selected virtual hardware version. Administrators can set specific hardware versions on virtual machines to standardize testing and deployment across the environment, providing a consistent baseline for workload portability.
+For container orchestration, VCF provides VMware Kubernetes Service, which uses the standard Kubernetes API and supports standard Container Network Interface (CNI) plugins. NSX integrates with Kubernetes clusters through the Antrea CNI and NSX Container Plugin (NCP), with NCP running in a container and communicating with NSX Manager and the Supervisor control plane. VCF supports multiple container cluster types including Kubernetes, OpenShift, AKS, EKS, GKE, and TKGm, providing broad interoperability with external container platforms. VKS ClusterClass resources carry kubernetes.vmware.com/max-version-supported and kubernetes.vmware.com/min-version-supported labels, making version compatibility constraints explicit and inspectable through standard Kubernetes tooling; administrators can list available VKS releases and review these constraints using the command-line interface before performing cluster updates. The Kubernetes cloud-controller-manager pattern, which VKS follows, isolates provider-specific code from core Kubernetes components through the CloudProvider interface, creating an architectural boundary that separates VMware-specific integrations from standard Kubernetes behavior and supports auditability of custom changes. When updating VKS clusters, the platform performs pre-checks and enforces compliance with compatibility requirements, reducing the risk of interoperability failures from format or version mismatches.
+Identity federation uses standard protocols: VCF SSO supports SAML 2.0 and OpenID Connect (OIDC) for integration with external identity providers such as Okta, Microsoft Entra ID, Ping Identity, and Microsoft ADFS. VCF Automation also supports importing provider users from SAML, OIDC, or VCF SSO identity providers.
+VCF Automation provides a structured blueprint format (formatVersion 2) with defined inputs and resources sections for specifying virtual machine and infrastructure component configurations. Cloud templates can be versioned and released to a catalog, with a dedicated API endpoint for creating new versions that captures change log entries, descriptions, release status, and version numbers. This versioning capability provides a mechanism for documenting changes to deployment templates over time. VCF Automation also supports importing AWS CloudFormation templates, allowing cloud administrators to create catalog items from both VCF-native templates and CloudFormation templates for deployment across cloud vendor regions or local datastores.
+VKS Cluster Management Security Policies support export of custom policy template definitions in YAML format for offline editing, version control, and re-import across the VKS cluster estate, accessible through either the VCF Automation API or portal interface. This capability applies the same change-documentation approach used for cloud templates to Kubernetes security policy configurations, enabling organizations to track and review customizations to cluster security posture as versioned, auditable artifacts. VKS cluster management also provisions add-ons using standardized defaults when the Latest compatible version option is selected, applying consistent configuration baselines across the cluster estate; platform teams can standardize on a curated collection of add-ons to maintain operationally consistent VKS clusters across the environment.
+VCF Operations tracks configuration drift across vCenter instances and vSphere clusters, comparing current settings against desired-state templates. Configuration drift templates can be integrated with source control repositories for versioning, auditing, and change control with reviews. Drift reports show historical changes by date, resource, and template, and administrators can trace configuration changes back to specific users and timestamps.
+While VCF provides these standardized format capabilities, container interoperability, identity federation, and change-tracking mechanisms, the control also requires organizational governance processes to mandate the use of industry-recognized formats, review custom changes, and enforce interoperability requirements with cloud providers. These policy and procedural requirements fall outside the scope of the platform itself.</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -1175,12 +1167,15 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>VCF contributes to AI implementation documentation by providing documented compute and hardware resource requirements, event log collection mechanisms, and infrastructure configuration references that support the documentation of AI deployment environments. VCF's compatibility guides document supported hardware, VCF Operations tracks infrastructure configuration, and VCF Log Management documents the event collection architecture.
-Documenting AI model architecture, training methodology, and decision logic is outside VCF's scope.
-VMware Private AI Services (PAIS), formerly Private AI Services, provides documentation and platform features that address several of the listed implementation documentation requirements. For computational and hardware resource requirements (item 6), the platform documents the system architecture of PAIS deployments, including GPU-accelerated workload domain requirements, vGPU profile configurations, VM class definitions for AI workloads, and the NVIDIA GPU and driver compatibility requirements. VI administrators configure vGPU-based VM classes that define the GPU resource allocations available to AI workloads. The PAIS catalog items in VCF Automation, including AI Workstation, DSM Database, Triton Inferencing Server, and AI Kubernetes Cluster, document the components users can provision in selected namespaces, and the deployment Overview tab summarizes the installed software and the access points for the application, services, and workstation VM. PAIS setup is documented for both connected and disconnected (air-gapped) deployment models, with a Harbor registry in the Supervisor or another OCI-compliant registry used to store validated ML models.
-For event logging mechanisms (item 8), the platform documents multiple logging and telemetry capabilities. Deep Learning VMs record cloud-init script logs in /var/log/dl.log and GPU driver installation logs in /var/log/gpu-install.log, and they provide JupyterLab instances and console logs for verifying component installation and operation. The vLLM inference server logging level is configurable through the VLLM_LOGGING_LEVEL environment variable. PAIS Controller pod metrics are exposed at a Prometheus endpoint on the pais-controller-manager service and are integrated into observability platforms through Telegraf configuration in the Supervisor instance, with VCF Operations as the documented consuming platform. Deep Learning VMs also expose vGPU performance metrics through Prometheus. PAIS supports LLM traces collection in an OpenTelemetry Collector by configuring the spec.observability.llmTraces section of the PAISConfiguration custom resource. Knowledge Base operations track crawled documents, new documents found, deleted documents, modified documents requiring embeddings updates, and skipped documents, and record timing metrics for download, embedding generation, and the overall index operation.
-For human oversight measures (item 5) and for interpreting outputs (items 4 and 5), MLOps engineers analyze LLM traces and Prometheus metrics to inspect agent execution flow across components and knowledge base indexing. The PAIS Agent Builder maintains a list of approved tools for use in AI agents and requires examination and approval of MCP server tools and capabilities before they are used by agents. Knowledge Bases are created with linked data sources such as Microsoft SharePoint sites and Amazon S3-compatible stores, which gives implementers a documented data lineage for retrieval-augmented generation outputs. Access to PAIS is controlled through OIDC authorized groups, where user accounts must be members of specified groups to consume the service, and personal access tokens generated from user account settings provide programmatic access to Knowledge Bases and data sources.
-Requirements 1 (provider contact details), 2 (characteristics, capabilities, and limitations of the AI system), 3 (errata from initial conformity assessment), and 7 (projected useable lifetime) are documentation obligations carried by model vendors and the deploying organization rather than by the infrastructure platform. PAIS supplies registry and catalog mechanisms that organizations can attach revision and provenance metadata to, but the substantive documentation content for those items is outside the platform's scope.</t>
+          <t>VCF provides several technical capabilities that support the use of industry-recognized virtualization formats, standardized deployment mechanisms, and change-tracking processes, helping organizations maintain interoperability across their cloud infrastructure.
+VCF natively supports the Open Virtualization Format (OVF), an industry standard that describes virtual machine image metadata in an XML format. OVF provides a vendor-neutral, portable way to package and distribute virtual machines, enabling interoperability between different virtualization platforms and cloud environments. OVF templates can be captured from virtual machines or vApps and stored in content libraries for consistent deployment. Content libraries support importing .ovf and .ova files, and the deployment specification for these templates supports optional guest operating system and hardware customization specifications applied during the deployment process. OVF templates from content libraries also become available in Kubernetes namespaces as VM images, allowing DevOps teams to self-service virtual machine provisioning through standard Kubernetes tooling. VMware Kubernetes Service (VKS) distributes Kubernetes node images as vSphere Kubernetes releases (VKrs) in the Open Virtualization Appliance (OVA) format, versioned according to standard Kubernetes versioning conventions. Each VKr documents its OS base (PhotonOS or Ubuntu) together with any vSphere-specific customizations and optimizations, making the scope of custom changes explicit and reviewable; legacy VKrs carry explicit backward-compatibility bounds to prior vSphere versions rather than leaving compatibility scope implicit. The VCF Image Baker supports customization of virtual machine hardware version through configurable OVF properties at build time, allowing organizations to produce node images aligned with their hardware baseline requirements. Guest operating system customization specifications are also stored in XML format and can be exported and imported through the VMware vCenter Customization Specification Manager, providing a portable mechanism for sharing standardized guest OS configurations across vCenter instances.
+VCF enforces standardized virtual hardware through a defined set of hardware versions. The HardwareTypes.Version class defines the valid hardware versions available for virtual machine configuration, and virtual machine CPU and memory configuration ranges are constrained based on the guest operating system and the selected virtual hardware version. Administrators can set specific hardware versions on virtual machines to standardize testing and deployment across the environment, providing a consistent baseline for workload portability.
+For container orchestration, VCF provides VMware Kubernetes Service, which uses the standard Kubernetes API and supports standard Container Network Interface (CNI) plugins. NSX integrates with Kubernetes clusters through the Antrea CNI and NSX Container Plugin (NCP), with NCP running in a container and communicating with NSX Manager and the Supervisor control plane. VCF supports multiple container cluster types including Kubernetes, OpenShift, AKS, EKS, GKE, and TKGm, providing broad interoperability with external container platforms. VKS ClusterClass resources carry kubernetes.vmware.com/max-version-supported and kubernetes.vmware.com/min-version-supported labels, making version compatibility constraints explicit and inspectable through standard Kubernetes tooling; administrators can list available VKS releases and review these constraints using the command-line interface before performing cluster updates. The Kubernetes cloud-controller-manager pattern, which VKS follows, isolates provider-specific code from core Kubernetes components through the CloudProvider interface, creating an architectural boundary that separates VMware-specific integrations from standard Kubernetes behavior and supports auditability of custom changes. When updating VKS clusters, the platform performs pre-checks and enforces compliance with compatibility requirements, reducing the risk of interoperability failures from format or version mismatches.
+Identity federation uses standard protocols: VCF SSO supports SAML 2.0 and OpenID Connect (OIDC) for integration with external identity providers such as Okta, Microsoft Entra ID, Ping Identity, and Microsoft ADFS. VCF Automation also supports importing provider users from SAML, OIDC, or VCF SSO identity providers.
+VCF Automation provides a structured blueprint format (formatVersion 2) with defined inputs and resources sections for specifying virtual machine and infrastructure component configurations. Cloud templates can be versioned and released to a catalog, with a dedicated API endpoint for creating new versions that captures change log entries, descriptions, release status, and version numbers. This versioning capability provides a mechanism for documenting changes to deployment templates over time. VCF Automation also supports importing AWS CloudFormation templates, allowing cloud administrators to create catalog items from both VCF-native templates and CloudFormation templates for deployment across cloud vendor regions or local datastores.
+VKS Cluster Management Security Policies support export of custom policy template definitions in YAML format for offline editing, version control, and re-import across the VKS cluster estate, accessible through either the VCF Automation API or portal interface. This capability applies the same change-documentation approach used for cloud templates to Kubernetes security policy configurations, enabling organizations to track and review customizations to cluster security posture as versioned, auditable artifacts. VKS cluster management also provisions add-ons using standardized defaults when the Latest compatible version option is selected, applying consistent configuration baselines across the cluster estate; platform teams can standardize on a curated collection of add-ons to maintain operationally consistent VKS clusters across the environment.
+VCF Operations tracks configuration drift across vCenter instances and vSphere clusters, comparing current settings against desired-state templates. Configuration drift templates can be integrated with source control repositories for versioning, auditing, and change control with reviews. Drift reports show historical changes by date, resource, and template, and administrators can trace configuration changes back to specific users and timestamps.
+While VCF provides these standardized format capabilities, container interoperability, identity federation, and change-tracking mechanisms, the control also requires organizational governance processes to mandate the use of industry-recognized formats, review custom changes, and enforce interoperability requirements with cloud providers. These policy and procedural requirements fall outside the scope of the platform itself.</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -1205,10 +1200,12 @@
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) uses secure protocols for all data movement and management communications in its disaster recovery and replication operations.
-All replication traffic between protected and recovery sites is protected using TLS. Starting with vSphere Replication 9.0.3 and later, network encryption of replication traffic is mandatory for both new and existing replications. For configurations on earlier versions, network encryption is available as a configurable option during replication setup.
-PNR uses TLS certificates and private keys to protect network communications and authenticate with other servers. An SSL/TLS certificate is required as the endpoint certificate for all TLS connections established to the PNR server, and custom certificates must meet specific product-defined requirements. The PNR Appliance supports importing CA-signed server certificates in .pem format through its management interface. Administrators can configure the minimum TLS protocol version through the envoy-proxy-config.json file.
-All communications between PNR and VMware vCenter instances take place over TLS connections, covering control plane traffic used to configure, monitor, and manage replication pairs, protection groups, and recovery plans. The VCF Operations Management Pack for PNR uses HTTPS on port 443 when connecting to the PNR appliance. The ransomware recovery component uses TLS for secure communications with connected systems.</t>
+          <t>VCF Protection and Recovery (PNR) uses industry-recognized formats and standards throughout its architecture, contributing to the interoperability requirements this control addresses.
+For storage integration, PNR's Virtual Volumes support relies on VMware APIs for Storage Awareness (VASA). VASA providers, developed by third-party storage vendors, mediate communication between VMware vCenter and the underlying storage system. PNR requires that these VASA providers be registered in vCenter before a Virtual Volumes environment can be used with PNR operations. Storage characteristics reported by the Virtual Volumes provider appear in the VM Storage Policies interface, allowing administrators to create storage policies that reflect the capabilities of the underlying storage hardware. Through this VASA interface, Virtual Volumes supports the full range of PNR operations: replication, test recovery, test cleanup, planned migration, disaster recovery, and reprotect.
+PNR exposes a REST API Gateway with documented endpoints for configuration and automation. The Protection and Recovery Server REST API provides endpoints to export configuration on demand and adjust export settings. A Configuration Import/Export Tool with schema support enables programmatic configuration management across sites, supporting consistent configuration of PNR infrastructure.
+PNR integrates with VCF Operations through the VCF Operations orchestrator Plug-In for Protection and Recovery. This plug-in provides automated workflows to convert virtual machines to replicated state, manage IP customization rules, and administer PNR infrastructure through the VCF Operations orchestrator's standard workflow engine.
+PNR deployments can span multiple cloud regions and include both on-premises and cloud-based site pairs, supporting recovery operations across hybrid environments that may involve multiple cloud providers or data centers.
+The underlying VCF platform provides additional standardization through OVF template management, VMware Kubernetes Service API support, SAML 2.0 and OIDC identity federation, CNI-compatible container networking, and configuration drift tracking. These are VCF platform capabilities rather than PNR-native features.</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
@@ -1294,12 +1291,12 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) supports network security monitoring through multiple integrated capabilities that contribute to enterprise-wide monitoring frameworks.
-Security Intelligence, hosted on the Security Services Platform (SSP), provides continuous visibility into network traffic flows across protected workloads. It monitors flows between application pairs, updates the Policy Protection Status for each application to indicate that flows are being monitored, and continuously detects new flows between environment pairs, alerting administrators to unauthorized or unexpected traffic. The Monitor &amp; Plan Overview page presents a consolidated view of pending actions, data collection activity status, network security posture, flow trends, and a summary of suspicious traffic. The Security Intelligence Recommendations monitoring capability checks for changes in the scope of monitored entities every hour when the Monitoring toggle is enabled, allowing administrators to keep policy recommendations current as environments evolve. Segmentation Monitoring provides dedicated views of application and infrastructure flows with configurable time ranges spanning from the last hour to the last month, and displays flows related to detected infrastructure servers in a specified time interval.
-The Network Detection and Response (NDR) Sensor checks the status of activated detection features every 15 minutes and updates its configuration accordingly, supporting sustained threat detection coverage. NDR Sensor health status monitoring tracks whether key components, including network traffic capture, file analysis, and data transmission, are operating properly. The NDR Sensor also sends alerts notifying administrators of conditions such as services being down, high CPU, memory, or disk usage, packet drops, or missed heartbeats. NDR provides role-based access control covering triage operations such as viewing detections and campaigns, as well as SIEM configuration management.
-The Security Services Platform monitors its own health, with Yellow or Red health status indicators displayed when issues occur in subcomponents. SSP monitoring tracks the status of the flow clustering job that runs every hour and reports suspicious traffic detector execution status after each run, with values such as SUCCESS, NOT_ENOUGH_BASELINE, and FAILURE.
-The Security dashboard provides a consolidated view for monitoring and configuring security features across network workloads. In federated deployments, the Global Manager provides centralized event management and monitoring for malicious IP blocking activity across all Local Managers.
-vDefend generates Unified Security Logs that VCF Log Management can collect and analyze. These logs cover Distributed Firewall, Gateway Firewall, Identity Firewall, FQDN Analysis, TLS Inspection, Intrusion Detection/Prevention System (IDPS), and URL Filtering activity. Broader log aggregation and SIEM correlation for enterprise-wide monitoring remain the responsibility of the SIEM and logging infrastructure deployed alongside vDefend.</t>
+          <t>VMware vDefend provides event log generation and monitoring capabilities across its security components in 9.1, directly supporting anomaly detection and assessment within the network security domain.
+The IDS/IPS subsystem generates detailed security event logs for event analysis. Remote syslog must be configured on ESX hosts to receive IDS/IPS events exported directly from those hosts; the `ids_events_to_syslog` setting controls whether IDS/IPS events are forwarded to external syslog consumers (the default is disabled). vDefend components write log data to /var/log, with syslog messages conforming to RFC 5424 on vDefend appliances and RFC 3164 on ESX hosts, enabling consistent ingestion by syslog-compatible platforms. The Security Explorer Computes view in Security Intelligence provides a full record of all IDS/IPS events for analysis over a 30-day timeframe. Security Intelligence also provides a View Full Event History capability that displays all events associated with a given signature ID along with their intrusion severity. The Threat Event Monitoring dashboard in Security Services Platform displays the trend in intrusion events over time, categorized by Intrusion Severity, giving security teams visibility into detection activity patterns.
+Malware Prevention Service generates structured event logs with detailed metadata per file analysis event. Event log fields include the verdict (BENIGN, malicious, or other classification status), a numeric risk score, malware classification, malware family, error codes and messages, HTTP domain, HTTP method, user agent, file upload status, submission status, analysis completion status, and gateway identification. File event statistics appear on the Monitor &amp; Plan &gt; Overview &gt; Threat Monitoring dashboard in Security Services Platform, with graphs covering a configurable time period (defaulting to the last hour).
+Network Detection and Response (NDR) generates and sends event logs to a SIEM endpoint when a detection event occurs, enabling integration with external correlation and reporting platforms.
+The Security Services Platform Monitor &amp; Plan Overview dashboard provides a view of security posture that includes the latest security segmentation report, flow trends, a summary of detected suspicious traffic events, pending actions, and current settings requiring attention. Security Intelligence generates bar graphs showing the number of anomalies detected, categorized by severity. The Policy Recommendations section tracks Security Intelligence recommendations with status indicators such as Ready to Publish, allowing security teams to act on recommended policy changes.
+vDefend Identity Firewall Event Log Sources can be integrated with VCF Log Management for centralized logging and monitoring. VCF Log Management supports Top-N queries using Interactive Analytics, enabling report generation from the aggregated log streams that vDefend supplies. VCF Log Management handles organization-level scheduled report generation, while vDefend provides the network-security-specific event data and dashboards that feed those reporting workflows.</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -1322,14 +1319,12 @@
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) contributes to enterprise-wide monitoring controls through a layered set of observability capabilities covering database health, infrastructure compliance, and event-driven alerting.
-DSM provides a built-in monitoring framework that tracks database instance health across multiple dimensions. From the Monitoring tab in the DSM UI or the vSphere Client, administrators and authorized users can view real-time and historical metrics for database VMs, including CPU Health, Data Disk Health, System Disk Health, Max Connections, Active Connections, Write Throughput, Read Throughput, Thread Resource Utilization, Slow Queries per Second, InnoDB Buffer Usage, and InnoDB Reads and Writes. The Monitoring page defaults to the last three hours of aggregated metric data, with the time range adjustable through the Time Range Last dropdown. This visibility supports detection of resource contention, performance degradation, and connectivity anomalies at the database layer.
-DSM's alert framework provides configurable thresholds for warning and critical conditions on key health indicators. Administrators and users can set separate warning and critical thresholds for CPU Health, Data Disk Health, System Disk Health, and Max Connections parameters. When thresholds are exceeded, DSM generates typed alerts such as Database Engine Health, Custom Config Health, and Backup Storage Health alerts. DSM monitors database replication status and raises an alert when a secondary database is not replicating data from the primary. DSM also raises an alert when metrics are no longer being received from a cluster, supporting detection of monitoring gaps. Alerts can be activated or deactivated per data service through the "Enable Alerts for DB Alert" setting, providing granular control over which databases are subject to active alerting. For each alert, DSM provides mitigation suggestions to help administrators resolve issues without disrupting database services.
-In addition to database-level alerts, DSM generates global infrastructure alerts that surface vCenter integration and infrastructure policy issues. These include INFRASTRUCTURE_POLICY_VC_ALARMS, raised when vCenter resource alarms are active; INFRASTRUCTURE_POLICY_CLUSTER_COMPLIANT and INVALID_SUPERVISOR_INFRASTRUCTURE_POLICY_STATUS, which reflect cluster compliance state; VCENTER_CONNECTIVITY, raised when vCenter connectivity fails and triggering troubleshooting steps that include verifying connectivity and checking authentication logs; and LicensingNotUpdated and vCenterBinding API status alerts that surface license and API integration conditions. A Global Alerts page in the DSM UI provides a centralized view of these alerts during and after installation and ongoing operation.
-In 9.1, DSM integrates with VCF Operations to extend observability beyond the DSM UI. When configured, VCF Operations automatically discovers and monitors PostgreSQL and MySQL clusters in the Ready state and displays a Data Services View dashboard showing active alerts and inventory items. VCF Operations presents performance data across three levels: cluster-level for overall health, node-level for infrastructure resource use, and database-level for KPIs including Active Connections, Commits, Rollbacks, and Deadlocks. This integration requires configuring the connection between DSM and VCF Operations before use.
-DSM also adds SQL Server as a supported database type, with dedicated monitoring through an integrated InfluxDB instance and Telegraf agents deployed across the provider appliance and SQL Server workload clusters. The monitoring framework supports metrics-based and status-condition-based alerts for SQL Server, covering database engine degradation, non-operational status, and automated or transaction log backup failure conditions.
-DSM supports event notification to external systems through a webhook integration. Webhooks transmit alert notifications containing the triggered date, triggered time, triggered user email, task status, previous status, and task type. This allows DSM alerts to feed into centralized monitoring or incident management platforms maintained by the organization. DSM generates plug-in registration logs that administrators can review for vCenter connectivity errors, and DSM's troubleshooting guidance directs administrators to review active vCenter infrastructure alarms and resolve underlying issues identified through the alert system.
-Enterprise-wide monitoring requires organizational decisions about monitoring architecture, log aggregation platforms, alerting policies, and operational response procedures that lie outside DSM's scope. DSM provides the data and integration points; the organization must determine how those signals are collected, correlated, and acted upon across the broader environment.</t>
+          <t>VMware Data Services Manager (DSM) provides event log generation and reporting capabilities that support detection and assessment of anomalous activities within the database-as-a-service layer.
+DSM's primary audit interface is the System Audit Events view, accessible through the System Audit section in the Provider UI. This view is the only location in the DSM interface where administrators can track non-database-related operations and tasks. Each audit entry records a Component field identifying the DSM component that performed the operation, an Event Type field identifying the nature of the audited event, Event Details providing operation-specific information, Event Time in UTC, and a Status field indicating the outcome of the event. The Source field records either a user identifier (Email ID) for user-initiated events or "System" for events initiated by DSM without user intervention, enabling attribution of each audit record to a specific actor. Standard Kubernetes audit events are also captured through the Gateway Audit Logs capability.
+Audit events can be exported in CSV or XLSX format using the ACTIONS dropdown menu in the System Audit Events view. Exports include all events visible to the requesting user regardless of page size, covering the Component, Event Type, Event Details, Event Time (UTC), Status, and Source fields. These exports can be brought into external reporting and analysis tools to support audit review and anomaly assessment.
+For persistent retention, DSM archives gateway audit log files periodically to an S3 repository subpath when a default S3 provider log repository is configured. Audit log files are also stored locally on the Provider VM at /var/log/tdm/provider/audit/ in files named with a gateway-audit-timestamp.log format, supporting direct access for investigation. Support bundles can be generated and downloaded to aggregate control plane and data plane logs from a database cluster for diagnosis. The Provider VM also includes a System Logs capability for managing system log collection.
+DSM provides operational monitoring that can surface indicators of abnormal behavior. The Monitoring tab for database instances displays metrics including Active Connections, Data Disk Usage, Write Throughput, Read Throughput, Thread Resource Utilization, Slow Queries per Second, InnoDB Buffer Usage %, InnoDB Reads and Writes, and Command Reads and Writes, with the time range adjustable through the Time Range Last dropdown. The Alerts pane in the Monitoring tab surfaces triggered alerts. DSM raises metrics-based alerts when metrics are successfully collected from a database cluster, status-condition-based alerts for critical failure conditions including database engine degradation and backup failures, and real-time alerts for resource or connectivity issues to support root cause identification. Webhook-based alerting supports integration with external notification systems for threshold-triggered database monitoring events. DSM can also be monitored through VCF Operations for additional troubleshooting and status visibility.
+Satisfying this control fully requires organizational processes to review exported audit data and monitoring output, establish baselines for normal activity, and investigate deviations. DSM does not include built-in anomaly detection, correlation, or security information and event management capabilities. Organizations typically forward DSM logs to a centralized log management platform for automated detection and reporting at scale.</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr">
